--- a/materials/record-templates/Electrochemical_Record_Template_v1_example_filled.xlsx
+++ b/materials/record-templates/Electrochemical_Record_Template_v1_example_filled.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Record" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Record" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -460,7 +460,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Electrochemical experiment record · 按导师模板 B 区设计（详见 docs/record-template-design.md）</t>
+          <t>电化学（无分室）实验记录 · 行级初始浓度长表（2026-10-17 重设计）</t>
         </is>
       </c>
     </row>
@@ -474,14 +474,14 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>实验编号 (Experiment ID)：RES-20260929-003</t>
+          <t>实验编号 (Experiment ID)：RES-20261017-001</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>实验日期 (Date)：2026-09-29</t>
+          <t>实验日期 (Date)：2026-10-17</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>电解液 (Electrolyte)：NaCl 500 mg/L</t>
+          <t>电解液 (Electrolyte)：NaCl 100-300 mg/L</t>
         </is>
       </c>
     </row>
@@ -537,274 +537,476 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>初始浓度 (mg/L)：100</t>
+          <t>温度 (degC)：25</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>温度 (degC)：25</t>
+          <t>电解池配置 (Cell configuration)：Single undivided cell, 2 cm spacing</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>电解池配置 (Cell configuration)：Single cell, 2 cm spacing</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
           <t>备注 / 检测仪器：IC (Dionex Aquion)</t>
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Cl 测量数据</t>
+        </is>
+      </c>
+    </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Cl 测量数据</t>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Time (s)</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Initial Concentration (mg/L)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Potential (V)</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Current (A)</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Concentration (mg/L)</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>pH</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>Time (s)</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Potential (V)</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Current (A)</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Concentration (mg/L)</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>pH</t>
-        </is>
+      <c r="A23" t="n">
+        <v>0</v>
+      </c>
+      <c r="B23" t="n">
+        <v>100</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E23" t="n">
+        <v>100</v>
+      </c>
+      <c r="F23" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="B24" t="n">
-        <v>1.2</v>
+        <v>100</v>
       </c>
       <c r="C24" t="n">
-        <v>0.52</v>
+        <v>1.2</v>
       </c>
       <c r="D24" t="n">
-        <v>100</v>
+        <v>0.5</v>
       </c>
       <c r="E24" t="n">
-        <v>6.5</v>
+        <v>78</v>
+      </c>
+      <c r="F24" t="n">
+        <v>6.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
+        <v>120</v>
+      </c>
+      <c r="B25" t="n">
+        <v>100</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="E25" t="n">
         <v>60</v>
       </c>
-      <c r="B25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D25" t="n">
-        <v>88</v>
-      </c>
-      <c r="E25" t="n">
-        <v>6.8</v>
+      <c r="F25" t="n">
+        <v>7.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="B26" t="n">
-        <v>1.2</v>
+        <v>100</v>
       </c>
       <c r="C26" t="n">
-        <v>0.47</v>
+        <v>1.2</v>
       </c>
       <c r="D26" t="n">
-        <v>74</v>
+        <v>0.44</v>
       </c>
       <c r="E26" t="n">
-        <v>7.2</v>
+        <v>46</v>
+      </c>
+      <c r="F26" t="n">
+        <v>7.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="B27" t="n">
-        <v>1.2</v>
+        <v>100</v>
       </c>
       <c r="C27" t="n">
-        <v>0.44</v>
+        <v>1.2</v>
       </c>
       <c r="D27" t="n">
-        <v>61</v>
+        <v>0.42</v>
       </c>
       <c r="E27" t="n">
-        <v>7.6</v>
+        <v>35</v>
+      </c>
+      <c r="F27" t="n">
+        <v>7.7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="B28" t="n">
-        <v>1.2</v>
+        <v>100</v>
       </c>
       <c r="C28" t="n">
-        <v>0.41</v>
+        <v>1.2</v>
       </c>
       <c r="D28" t="n">
-        <v>49</v>
+        <v>0.4</v>
       </c>
       <c r="E28" t="n">
-        <v>8</v>
+        <v>27</v>
+      </c>
+      <c r="F28" t="n">
+        <v>7.9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="B29" t="n">
-        <v>1.2</v>
+        <v>200</v>
       </c>
       <c r="C29" t="n">
-        <v>0.39</v>
+        <v>1.2</v>
       </c>
       <c r="D29" t="n">
-        <v>38</v>
+        <v>0.58</v>
       </c>
       <c r="E29" t="n">
-        <v>8.4</v>
+        <v>200</v>
+      </c>
+      <c r="F29" t="n">
+        <v>6.4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>360</v>
+        <v>60</v>
       </c>
       <c r="B30" t="n">
-        <v>1.2</v>
+        <v>200</v>
       </c>
       <c r="C30" t="n">
-        <v>0.36</v>
+        <v>1.2</v>
       </c>
       <c r="D30" t="n">
-        <v>29</v>
+        <v>0.55</v>
       </c>
       <c r="E30" t="n">
-        <v>8.699999999999999</v>
+        <v>165</v>
+      </c>
+      <c r="F30" t="n">
+        <v>6.6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>420</v>
+        <v>120</v>
       </c>
       <c r="B31" t="n">
-        <v>1.2</v>
+        <v>200</v>
       </c>
       <c r="C31" t="n">
-        <v>0.34</v>
+        <v>1.2</v>
       </c>
       <c r="D31" t="n">
-        <v>21</v>
+        <v>0.52</v>
       </c>
       <c r="E31" t="n">
-        <v>8.9</v>
+        <v>136</v>
+      </c>
+      <c r="F31" t="n">
+        <v>6.9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>480</v>
+        <v>180</v>
       </c>
       <c r="B32" t="n">
-        <v>1.2</v>
+        <v>200</v>
       </c>
       <c r="C32" t="n">
-        <v>0.32</v>
+        <v>1.2</v>
       </c>
       <c r="D32" t="n">
-        <v>15</v>
+        <v>0.49</v>
       </c>
       <c r="E32" t="n">
-        <v>9.1</v>
+        <v>112</v>
+      </c>
+      <c r="F32" t="n">
+        <v>7.1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>600</v>
+        <v>240</v>
       </c>
       <c r="B33" t="n">
-        <v>1.2</v>
+        <v>200</v>
       </c>
       <c r="C33" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="D33" t="n">
-        <v>9.5</v>
+        <v>0.47</v>
       </c>
       <c r="E33" t="n">
-        <v>9.300000000000001</v>
+        <v>93</v>
+      </c>
+      <c r="F33" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>300</v>
+      </c>
+      <c r="B34" t="n">
+        <v>200</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E34" t="n">
+        <v>78</v>
+      </c>
+      <c r="F34" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>0</v>
+      </c>
+      <c r="B35" t="n">
+        <v>300</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E35" t="n">
+        <v>300</v>
+      </c>
+      <c r="F35" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>60</v>
+      </c>
+      <c r="B36" t="n">
+        <v>300</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E36" t="n">
+        <v>256</v>
+      </c>
+      <c r="F36" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" t="n">
+        <v>120</v>
+      </c>
+      <c r="B37" t="n">
+        <v>300</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E37" t="n">
+        <v>218</v>
+      </c>
+      <c r="F37" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>180</v>
+      </c>
+      <c r="B38" t="n">
+        <v>300</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="E38" t="n">
+        <v>186</v>
+      </c>
+      <c r="F38" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>240</v>
+      </c>
+      <c r="B39" t="n">
+        <v>300</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E39" t="n">
+        <v>160</v>
+      </c>
+      <c r="F39" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>300</v>
+      </c>
+      <c r="B40" t="n">
+        <v>300</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E40" t="n">
+        <v>138</v>
+      </c>
+      <c r="F40" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>填写说明</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>1) 把数据块标题中的【离子名】替换为实际目标离子（如 SO4、Cl、Na）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>2) 数据从表头下方第一行开始连续填写，不要留空行；未测量的点留空（不要写 NA/ND）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>3) 多离子实验：复制整个数据块（标题行 + 表头行 + 数据行），每离子一块，块间保留 3 行空行。</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>4) 实验信息区每行只写在最左侧一格内，不要拆到多列。</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>5) 时间单位为秒 (s)；只记录原始测量值；电流密度、电荷量等由系统自动计算。</t>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>1) 把数据块标题中的【离子名】替换为实际目标离子（如 SO4、Cl、Na），保留【】括号。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>2) 同一数据块记录多个初始浓度（多轮实验）的结果：按轮次顺序连排，Initial Concentration 列每行填写该轮初始浓度；同一轮的时间序列从 0 开始连续记录。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>3) 块内不要留空行；不要把不同初始浓度并列成多列；未测量的点留空（不要写 NA/ND）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>4) 多离子实验：复制整个数据块（标题行 + 表头行 + 数据行），每离子一块，块间保留 3 行空行。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>5) 实验信息区每行只写在最左侧一格内，不要拆到多列。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>6) 时间单位为秒 (s)；只记录原始测量值；终浓度、去除率、电荷量、能耗等由系统按「离子 × 初始浓度」分组自动计算。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>7) 本表为无分室电解池设计；若实验有膜分室，请改用两室 / 三室 / 双极膜记录表。</t>
         </is>
       </c>
     </row>
